--- a/data/trans_orig/P16A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27095</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>50480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>79342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83553</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121133</t>
+          <t>120295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643855</t>
+          <t>643532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666917</t>
+          <t>665914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609648</t>
+          <t>609009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638226</t>
+          <t>640356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1261230</t>
+          <t>1262068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1298810</t>
+          <t>1298682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62366</t>
+          <t>61882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93166</t>
+          <t>92432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131686</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>136699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183034</t>
+          <t>185508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899434</t>
+          <t>899918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>928235</t>
+          <t>927571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>836707</t>
+          <t>837711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>875227</t>
+          <t>875961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1747159</t>
+          <t>1744685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1794967</t>
+          <t>1793494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>18967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40730</t>
+          <t>40664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133471</t>
+          <t>133926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637779</t>
+          <t>637845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658925</t>
+          <t>659542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>583297</t>
+          <t>583785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615935</t>
+          <t>616028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228879</t>
+          <t>1228424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267057</t>
+          <t>1267849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>35621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100908</t>
+          <t>99944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>141073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143743</t>
+          <t>144754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192657</t>
+          <t>194276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>881294</t>
+          <t>881338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>905750</t>
+          <t>906601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>894764</t>
+          <t>897539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>937704</t>
+          <t>938668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1788177</t>
+          <t>1786558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837091</t>
+          <t>1836080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188322</t>
+          <t>186644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>339971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413853</t>
+          <t>408540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>495709</t>
+          <t>499543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>588787</t>
+          <t>582131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3088221</t>
+          <t>3089899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3138565</t>
+          <t>3138832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2965344</t>
+          <t>2970657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3037902</t>
+          <t>3039226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6066954</t>
+          <t>6073610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6160032</t>
+          <t>6156198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34296</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60269</t>
+          <t>61878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>91859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131037</t>
+          <t>130299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>133930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182013</t>
+          <t>183057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643200</t>
+          <t>641591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669173</t>
+          <t>670232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566013</t>
+          <t>566751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>605011</t>
+          <t>605191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218506</t>
+          <t>1217462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1266428</t>
+          <t>1266589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55208</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88451</t>
+          <t>88643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137523</t>
+          <t>139743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183914</t>
+          <t>187389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203402</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260075</t>
+          <t>262658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>929496</t>
+          <t>929304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>962739</t>
+          <t>963632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>848270</t>
+          <t>844795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>894661</t>
+          <t>892441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1790056</t>
+          <t>1787473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1846729</t>
+          <t>1847933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56621</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95322</t>
+          <t>96179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137725</t>
+          <t>138278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133066</t>
+          <t>133275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182083</t>
+          <t>183822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701002</t>
+          <t>699950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729954</t>
+          <t>728899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639449</t>
+          <t>638896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681852</t>
+          <t>680995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1352714</t>
+          <t>1350975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1401731</t>
+          <t>1401522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>91536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143412</t>
+          <t>145993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192384</t>
+          <t>193792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212053</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272313</t>
+          <t>275850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856858</t>
+          <t>856203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891582</t>
+          <t>891113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>859517</t>
+          <t>858109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>908489</t>
+          <t>905908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1727327</t>
+          <t>1723790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1787587</t>
+          <t>1786709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198997</t>
+          <t>198349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>261076</t>
+          <t>262165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513093</t>
+          <t>507726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>597912</t>
+          <t>595880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>728374</t>
+          <t>732170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>840686</t>
+          <t>840872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3165703</t>
+          <t>3164614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3227782</t>
+          <t>3228430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2960397</t>
+          <t>2962429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3045216</t>
+          <t>3050583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6144402</t>
+          <t>6144216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6256714</t>
+          <t>6252918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48459</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98370</t>
+          <t>100436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138841</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133329</t>
+          <t>132917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181585</t>
+          <t>180418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626341</t>
+          <t>625180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>648929</t>
+          <t>649283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533998</t>
+          <t>532267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>574469</t>
+          <t>572403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1166054</t>
+          <t>1167221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1214310</t>
+          <t>1214722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74595</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120097</t>
+          <t>119141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165606</t>
+          <t>163171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174183</t>
+          <t>172348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229323</t>
+          <t>227288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947836</t>
+          <t>947129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>976918</t>
+          <t>977766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>877307</t>
+          <t>879742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922816</t>
+          <t>923772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1836021</t>
+          <t>1838056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1891161</t>
+          <t>1892996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35252</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62643</t>
+          <t>63064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>90912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129580</t>
+          <t>131827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>134000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181648</t>
+          <t>185287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696909</t>
+          <t>696488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>724300</t>
+          <t>724401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655431</t>
+          <t>653184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>696004</t>
+          <t>694099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1362915</t>
+          <t>1359276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1410682</t>
+          <t>1410563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85942</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144262</t>
+          <t>144876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195927</t>
+          <t>193568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209564</t>
+          <t>210591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>271030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851625</t>
+          <t>850272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882296</t>
+          <t>882026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>847852</t>
+          <t>850211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899517</t>
+          <t>898903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1710962</t>
+          <t>1710316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1771782</t>
+          <t>1770755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187163</t>
+          <t>184534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243107</t>
+          <t>240749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>495516</t>
+          <t>494082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>583035</t>
+          <t>583729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696759</t>
+          <t>699388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>802928</t>
+          <t>800588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3151243</t>
+          <t>3153601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3207187</t>
+          <t>3209816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2961507</t>
+          <t>2960813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3049026</t>
+          <t>3050460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6135964</t>
+          <t>6138304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6242133</t>
+          <t>6239504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97337</t>
+          <t>93605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138420</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158261</t>
+          <t>161238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209136</t>
+          <t>209322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555641</t>
+          <t>556005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>583493</t>
+          <t>583936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>586910</t>
+          <t>587225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>627993</t>
+          <t>631725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1151636</t>
+          <t>1151450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202511</t>
+          <t>1199534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88863</t>
+          <t>87876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>154800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190183</t>
+          <t>192396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161421</t>
+          <t>163053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276029</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1104001</t>
+          <t>1104988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1157109</t>
+          <t>1161963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768468</t>
+          <t>766255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>804966</t>
+          <t>803851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1875487</t>
+          <t>1876209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1990095</t>
+          <t>1988463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76704</t>
+          <t>75528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154319</t>
+          <t>154129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119392</t>
+          <t>116034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207552</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627976</t>
+          <t>629152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657800</t>
+          <t>658353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>779047</t>
+          <t>779237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>870858</t>
+          <t>878657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1430494</t>
+          <t>1428355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1518654</t>
+          <t>1522012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78176</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112352</t>
+          <t>112760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157979</t>
+          <t>160904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220299</t>
+          <t>222538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252021</t>
+          <t>249431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>319635</t>
+          <t>320066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848655</t>
+          <t>849554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>874633</t>
+          <t>872394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936953</t>
+          <t>934028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1702128</t>
+          <t>1701697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1769742</t>
+          <t>1772332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225782</t>
+          <t>222400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324905</t>
+          <t>320799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>478497</t>
+          <t>490632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>656282</t>
+          <t>660644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>775592</t>
+          <t>760517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>964118</t>
+          <t>961645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3134912</t>
+          <t>3139018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3234035</t>
+          <t>3237417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3055998</t>
+          <t>3051636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3233783</t>
+          <t>3221648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6207979</t>
+          <t>6210452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6396505</t>
+          <t>6411580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79342</t>
+          <t>78797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>84166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120295</t>
+          <t>123225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643532</t>
+          <t>643460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665914</t>
+          <t>666826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609009</t>
+          <t>609554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>640356</t>
+          <t>638861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262068</t>
+          <t>1259138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1298682</t>
+          <t>1298197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61882</t>
+          <t>61572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>93005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130682</t>
+          <t>133471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136699</t>
+          <t>135040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185508</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899918</t>
+          <t>900228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>927571</t>
+          <t>927619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>837711</t>
+          <t>834922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>875961</t>
+          <t>875388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1744685</t>
+          <t>1745921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1793494</t>
+          <t>1795153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>68677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100056</t>
+          <t>101783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94501</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>134276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637845</t>
+          <t>637950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659542</t>
+          <t>658722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>583785</t>
+          <t>582058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616028</t>
+          <t>615164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228424</t>
+          <t>1228074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267849</t>
+          <t>1269030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99944</t>
+          <t>99374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141073</t>
+          <t>140300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144754</t>
+          <t>142234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194276</t>
+          <t>193777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>881338</t>
+          <t>881210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>906601</t>
+          <t>906606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>897539</t>
+          <t>898312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938668</t>
+          <t>939238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1786558</t>
+          <t>1787057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1836080</t>
+          <t>1838600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>339971</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408540</t>
+          <t>412231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>499543</t>
+          <t>495382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>582131</t>
+          <t>586238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3089899</t>
+          <t>3089072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3138832</t>
+          <t>3140880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2970657</t>
+          <t>2966966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3039226</t>
+          <t>3036436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6073610</t>
+          <t>6069503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6156198</t>
+          <t>6160359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>61991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91859</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>130008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133930</t>
+          <t>133667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183057</t>
+          <t>180665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641591</t>
+          <t>641478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670232</t>
+          <t>669529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566751</t>
+          <t>567042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>605191</t>
+          <t>606166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1217462</t>
+          <t>1219854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1266589</t>
+          <t>1266852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54315</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88643</t>
+          <t>87237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139743</t>
+          <t>139834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187389</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202198</t>
+          <t>200361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262658</t>
+          <t>260669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>929304</t>
+          <t>930710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>963632</t>
+          <t>964769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>844795</t>
+          <t>843934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>892441</t>
+          <t>892350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1787473</t>
+          <t>1789462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1847933</t>
+          <t>1849770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96179</t>
+          <t>96915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138278</t>
+          <t>138017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133275</t>
+          <t>133565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183822</t>
+          <t>185307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>699950</t>
+          <t>698675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728899</t>
+          <t>729308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638896</t>
+          <t>639157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>680995</t>
+          <t>680259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1350975</t>
+          <t>1349490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1401522</t>
+          <t>1401232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>56270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91536</t>
+          <t>92984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145993</t>
+          <t>145902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193792</t>
+          <t>192174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212931</t>
+          <t>211690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275850</t>
+          <t>270915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856203</t>
+          <t>854755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891113</t>
+          <t>891469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>858109</t>
+          <t>859727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>905908</t>
+          <t>905999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1723790</t>
+          <t>1728725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1786709</t>
+          <t>1787950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198349</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>262165</t>
+          <t>259956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507726</t>
+          <t>515873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>595880</t>
+          <t>602809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>732170</t>
+          <t>727951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>840872</t>
+          <t>834702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3164614</t>
+          <t>3166823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3228430</t>
+          <t>3231509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2962429</t>
+          <t>2955500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3050583</t>
+          <t>3042436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6144216</t>
+          <t>6150386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6252918</t>
+          <t>6257137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>48763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100436</t>
+          <t>100645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140572</t>
+          <t>138892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132917</t>
+          <t>133713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180418</t>
+          <t>179726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>625180</t>
+          <t>626037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>649283</t>
+          <t>649314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>532267</t>
+          <t>533947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>572403</t>
+          <t>572194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167221</t>
+          <t>1167913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1214722</t>
+          <t>1213926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119141</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163171</t>
+          <t>165709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172348</t>
+          <t>171857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227288</t>
+          <t>230904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947129</t>
+          <t>947273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>977766</t>
+          <t>978020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>879742</t>
+          <t>877204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923772</t>
+          <t>923003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838056</t>
+          <t>1834440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1892996</t>
+          <t>1893487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35151</t>
+          <t>35745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>62961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90912</t>
+          <t>91045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131827</t>
+          <t>131997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134000</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185287</t>
+          <t>182486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696488</t>
+          <t>696591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>724401</t>
+          <t>723807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653184</t>
+          <t>653014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>694099</t>
+          <t>693966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1359276</t>
+          <t>1362077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1410563</t>
+          <t>1412706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144876</t>
+          <t>144606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193568</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210591</t>
+          <t>211620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271030</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850272</t>
+          <t>848090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882026</t>
+          <t>881645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>850211</t>
+          <t>848128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898903</t>
+          <t>899173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1710316</t>
+          <t>1711978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1770755</t>
+          <t>1769726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>186862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240749</t>
+          <t>243370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>494082</t>
+          <t>500061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>583729</t>
+          <t>586337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>699388</t>
+          <t>696469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>800588</t>
+          <t>802855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3153601</t>
+          <t>3150980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3209816</t>
+          <t>3207488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2960813</t>
+          <t>2958205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3050460</t>
+          <t>3044481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6138304</t>
+          <t>6136037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6239504</t>
+          <t>6242423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>70255</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>88084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>121213</t>
+          <t>129880</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93605</t>
+          <t>114020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138105</t>
+          <t>146230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>185390</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161238</t>
+          <t>179233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209322</t>
+          <t>222381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>571264</t>
+          <t>620455</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>556005</t>
+          <t>602626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>583936</t>
+          <t>634416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>604117</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>587225</t>
+          <t>587950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631725</t>
+          <t>620160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1175382</t>
+          <t>1224755</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1151450</t>
+          <t>1202508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1199534</t>
+          <t>1245656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64142</t>
+          <t>70343</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87876</t>
+          <t>87281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>172290</t>
+          <t>189313</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154800</t>
+          <t>170377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192396</t>
+          <t>209021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>236432</t>
+          <t>259655</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163053</t>
+          <t>230963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275307</t>
+          <t>286388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1128722</t>
+          <t>978574</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1104988</t>
+          <t>961636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1161963</t>
+          <t>993427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>786361</t>
+          <t>882161</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>766255</t>
+          <t>862453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>803851</t>
+          <t>901097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1915084</t>
+          <t>1860736</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1876209</t>
+          <t>1834003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1988463</t>
+          <t>1889428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60568</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>52993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75528</t>
+          <t>85442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>108984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154129</t>
+          <t>144207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>194854</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116034</t>
+          <t>171532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209691</t>
+          <t>221398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>10,62%</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>644112</t>
+          <t>734263</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629152</t>
+          <t>717631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658353</t>
+          <t>750080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>819949</t>
+          <t>686215</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>779237</t>
+          <t>668052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>878657</t>
+          <t>703275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1464061</t>
+          <t>1420478</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1428355</t>
+          <t>1393934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522012</t>
+          <t>1443800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>86,29%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>89,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>95904</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>80177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112760</t>
+          <t>117212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>195123</t>
+          <t>207236</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160904</t>
+          <t>185923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222538</t>
+          <t>230348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>288838</t>
+          <t>303139</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249431</t>
+          <t>274260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320066</t>
+          <t>331649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>833116</t>
+          <t>894158</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814071</t>
+          <t>872850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849554</t>
+          <t>909885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>899809</t>
+          <t>911805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>872394</t>
+          <t>888693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>934028</t>
+          <t>933118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1732925</t>
+          <t>1805965</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1701697</t>
+          <t>1777455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1772332</t>
+          <t>1834844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>222400</t>
+          <t>270968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>339187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>490632</t>
+          <t>613414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>660644</t>
+          <t>689803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>760517</t>
+          <t>906063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>961645</t>
+          <t>1009350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3177215</t>
+          <t>3227451</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3139018</t>
+          <t>3193575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3237417</t>
+          <t>3261794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3110238</t>
+          <t>3084482</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3051636</t>
+          <t>3047151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3221648</t>
+          <t>3123540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6287453</t>
+          <t>6311933</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6210452</t>
+          <t>6260366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6411580</t>
+          <t>6363653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
